--- a/Workplans/PROCUREMENT PLAN TEMPLATE 2026.xlsx
+++ b/Workplans/PROCUREMENT PLAN TEMPLATE 2026.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akama\OneDrive\Desktop\EGP work 2026-2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DSAS\Workplans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96C266D9-C963-4A0F-A54F-1FD357EC283B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{60FFBDEA-1C1B-4D5D-9E3E-9AA36C9CBEA9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -300,7 +299,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -469,6 +468,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -481,28 +492,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 3" xfId="2" xr:uid="{907E8B42-10B0-43AC-824F-95A477A42781}"/>
+    <cellStyle name="Comma 3" xfId="2"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -814,7 +809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B118225F-CE34-434D-ACAA-33FA5A5C6769}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T238"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -873,16 +868,16 @@
       <c r="L2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="15"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="25"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -897,22 +892,22 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14" t="s">
+      <c r="N3" s="24"/>
+      <c r="O3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="12" t="s">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12" t="s">
+      <c r="R3" s="22"/>
+      <c r="S3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="T3" s="12"/>
+      <c r="T3" s="22"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -2375,10 +2370,10 @@
       <c r="T68" s="6"/>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B69" s="17"/>
+      <c r="B69" s="27"/>
       <c r="C69" s="6"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
@@ -5343,328 +5338,327 @@
       <c r="T197" s="6"/>
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C200" s="22"/>
-      <c r="D200" s="22"/>
+      <c r="C200" s="16"/>
+      <c r="D200" s="16"/>
     </row>
     <row r="201" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A201" s="18" t="s">
+      <c r="A201" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B201" s="21" t="s">
+      <c r="B201" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C201" s="23"/>
-      <c r="D201" s="23"/>
+      <c r="C201" s="17"/>
+      <c r="D201" s="17"/>
     </row>
     <row r="202" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A202" s="19" t="s">
+      <c r="A202" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B202" s="19"/>
-      <c r="C202" s="23"/>
-      <c r="D202" s="24"/>
+      <c r="B202" s="13"/>
+      <c r="C202" s="17"/>
+      <c r="D202" s="18"/>
     </row>
     <row r="203" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A203" s="19" t="s">
+      <c r="A203" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B203" s="19"/>
-      <c r="C203" s="23"/>
-      <c r="D203" s="24"/>
+      <c r="B203" s="13"/>
+      <c r="C203" s="17"/>
+      <c r="D203" s="18"/>
     </row>
     <row r="204" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A204" s="19" t="s">
+      <c r="A204" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B204" s="19"/>
-      <c r="C204" s="23"/>
-      <c r="D204" s="24"/>
+      <c r="B204" s="13"/>
+      <c r="C204" s="17"/>
+      <c r="D204" s="18"/>
     </row>
     <row r="205" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="19" t="s">
+      <c r="A205" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B205" s="19"/>
-      <c r="C205" s="23"/>
-      <c r="D205" s="24"/>
+      <c r="B205" s="13"/>
+      <c r="C205" s="17"/>
+      <c r="D205" s="18"/>
     </row>
     <row r="206" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="19" t="s">
+      <c r="A206" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B206" s="19"/>
-      <c r="C206" s="23"/>
-      <c r="D206" s="24"/>
+      <c r="B206" s="13"/>
+      <c r="C206" s="17"/>
+      <c r="D206" s="18"/>
     </row>
     <row r="207" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A207" s="19" t="s">
+      <c r="A207" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B207" s="19"/>
-      <c r="C207" s="23"/>
-      <c r="D207" s="24"/>
+      <c r="B207" s="13"/>
+      <c r="C207" s="17"/>
+      <c r="D207" s="18"/>
     </row>
     <row r="208" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A208" s="19" t="s">
+      <c r="A208" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B208" s="19"/>
-      <c r="C208" s="23"/>
-      <c r="D208" s="24"/>
+      <c r="B208" s="13"/>
+      <c r="C208" s="17"/>
+      <c r="D208" s="18"/>
     </row>
     <row r="209" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A209" s="19" t="s">
+      <c r="A209" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B209" s="19"/>
-      <c r="C209" s="23"/>
-      <c r="D209" s="24"/>
+      <c r="B209" s="13"/>
+      <c r="C209" s="17"/>
+      <c r="D209" s="18"/>
     </row>
     <row r="210" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A210" s="19" t="s">
+      <c r="A210" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B210" s="19"/>
-      <c r="C210" s="23"/>
-      <c r="D210" s="24"/>
+      <c r="B210" s="13"/>
+      <c r="C210" s="17"/>
+      <c r="D210" s="18"/>
     </row>
     <row r="211" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A211" s="19" t="s">
+      <c r="A211" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B211" s="19"/>
-      <c r="C211" s="23"/>
-      <c r="D211" s="24"/>
+      <c r="B211" s="13"/>
+      <c r="C211" s="17"/>
+      <c r="D211" s="18"/>
     </row>
     <row r="212" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A212" s="19" t="s">
+      <c r="A212" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B212" s="19"/>
-      <c r="C212" s="23"/>
-      <c r="D212" s="24"/>
+      <c r="B212" s="13"/>
+      <c r="C212" s="17"/>
+      <c r="D212" s="18"/>
     </row>
     <row r="213" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A213" s="19" t="s">
+      <c r="A213" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B213" s="19"/>
-      <c r="C213" s="23"/>
-      <c r="D213" s="24"/>
+      <c r="B213" s="13"/>
+      <c r="C213" s="17"/>
+      <c r="D213" s="18"/>
     </row>
     <row r="214" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A214" s="19" t="s">
+      <c r="A214" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B214" s="19"/>
-      <c r="C214" s="23"/>
-      <c r="D214" s="24"/>
+      <c r="B214" s="13"/>
+      <c r="C214" s="17"/>
+      <c r="D214" s="18"/>
     </row>
     <row r="215" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A215" s="19" t="s">
+      <c r="A215" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B215" s="19"/>
-      <c r="C215" s="23"/>
-      <c r="D215" s="24"/>
+      <c r="B215" s="13"/>
+      <c r="C215" s="17"/>
+      <c r="D215" s="18"/>
     </row>
     <row r="216" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A216" s="19" t="s">
+      <c r="A216" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B216" s="19"/>
-      <c r="C216" s="23"/>
-      <c r="D216" s="24"/>
+      <c r="B216" s="13"/>
+      <c r="C216" s="17"/>
+      <c r="D216" s="18"/>
     </row>
     <row r="217" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A217" s="19" t="s">
+      <c r="A217" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B217" s="19"/>
-      <c r="C217" s="23"/>
-      <c r="D217" s="24"/>
+      <c r="B217" s="13"/>
+      <c r="C217" s="17"/>
+      <c r="D217" s="18"/>
     </row>
     <row r="218" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A218" s="19" t="s">
+      <c r="A218" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B218" s="19"/>
-      <c r="C218" s="23"/>
-      <c r="D218" s="24"/>
+      <c r="B218" s="13"/>
+      <c r="C218" s="17"/>
+      <c r="D218" s="18"/>
     </row>
     <row r="219" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A219" s="19" t="s">
+      <c r="A219" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B219" s="19"/>
-      <c r="C219" s="23"/>
-      <c r="D219" s="24"/>
+      <c r="B219" s="13"/>
+      <c r="C219" s="17"/>
+      <c r="D219" s="18"/>
     </row>
     <row r="220" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="19" t="s">
+      <c r="A220" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B220" s="19"/>
-      <c r="C220" s="23"/>
-      <c r="D220" s="24"/>
+      <c r="B220" s="13"/>
+      <c r="C220" s="17"/>
+      <c r="D220" s="18"/>
     </row>
     <row r="221" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="19" t="s">
+      <c r="A221" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B221" s="19"/>
-      <c r="C221" s="23"/>
-      <c r="D221" s="24"/>
+      <c r="B221" s="13"/>
+      <c r="C221" s="17"/>
+      <c r="D221" s="18"/>
     </row>
     <row r="222" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A222" s="19" t="s">
+      <c r="A222" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B222" s="19"/>
-      <c r="C222" s="23"/>
-      <c r="D222" s="24"/>
+      <c r="B222" s="13"/>
+      <c r="C222" s="17"/>
+      <c r="D222" s="18"/>
     </row>
     <row r="223" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A223" s="19" t="s">
+      <c r="A223" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B223" s="19"/>
-      <c r="C223" s="23"/>
-      <c r="D223" s="24"/>
+      <c r="B223" s="13"/>
+      <c r="C223" s="17"/>
+      <c r="D223" s="18"/>
     </row>
     <row r="224" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A224" s="19" t="s">
+      <c r="A224" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B224" s="19"/>
-      <c r="C224" s="23"/>
-      <c r="D224" s="24"/>
+      <c r="B224" s="13"/>
+      <c r="C224" s="17"/>
+      <c r="D224" s="18"/>
     </row>
     <row r="225" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A225" s="19" t="s">
+      <c r="A225" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B225" s="19"/>
-      <c r="C225" s="23"/>
-      <c r="D225" s="24"/>
+      <c r="B225" s="13"/>
+      <c r="C225" s="17"/>
+      <c r="D225" s="18"/>
     </row>
     <row r="226" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A226" s="20" t="s">
+      <c r="A226" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B226" s="19"/>
-      <c r="C226" s="23"/>
-      <c r="D226" s="24"/>
+      <c r="B226" s="13"/>
+      <c r="C226" s="17"/>
+      <c r="D226" s="18"/>
     </row>
     <row r="227" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A227" s="19" t="s">
+      <c r="A227" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B227" s="19"/>
-      <c r="C227" s="23"/>
-      <c r="D227" s="24"/>
+      <c r="B227" s="13"/>
+      <c r="C227" s="17"/>
+      <c r="D227" s="18"/>
     </row>
     <row r="228" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A228" s="19" t="s">
+      <c r="A228" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B228" s="19"/>
-      <c r="C228" s="23"/>
-      <c r="D228" s="24"/>
+      <c r="B228" s="13"/>
+      <c r="C228" s="17"/>
+      <c r="D228" s="18"/>
     </row>
     <row r="229" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A229" s="19" t="s">
+      <c r="A229" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B229" s="19"/>
-      <c r="C229" s="23"/>
-      <c r="D229" s="24"/>
+      <c r="B229" s="13"/>
+      <c r="C229" s="17"/>
+      <c r="D229" s="18"/>
     </row>
     <row r="230" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A230" s="19" t="s">
+      <c r="A230" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B230" s="19"/>
-      <c r="C230" s="23"/>
-      <c r="D230" s="24"/>
+      <c r="B230" s="13"/>
+      <c r="C230" s="17"/>
+      <c r="D230" s="18"/>
     </row>
     <row r="231" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A231" s="19" t="s">
+      <c r="A231" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B231" s="19" t="s">
+      <c r="B231" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C231" s="23"/>
-      <c r="D231" s="24"/>
+      <c r="C231" s="17"/>
+      <c r="D231" s="18"/>
     </row>
     <row r="232" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A232" s="19" t="s">
+      <c r="A232" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B232" s="19"/>
-      <c r="C232" s="23"/>
-      <c r="D232" s="24"/>
+      <c r="B232" s="13"/>
+      <c r="C232" s="17"/>
+      <c r="D232" s="18"/>
     </row>
     <row r="233" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A233" s="19" t="s">
+      <c r="A233" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B233" s="19"/>
-      <c r="C233" s="23"/>
-      <c r="D233" s="24"/>
+      <c r="B233" s="13"/>
+      <c r="C233" s="17"/>
+      <c r="D233" s="18"/>
     </row>
     <row r="234" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A234" s="19" t="s">
+      <c r="A234" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B234" s="19"/>
-      <c r="C234" s="23"/>
-      <c r="D234" s="24"/>
+      <c r="B234" s="13"/>
+      <c r="C234" s="17"/>
+      <c r="D234" s="18"/>
     </row>
     <row r="235" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A235" s="21" t="s">
+      <c r="A235" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B235" s="21"/>
-      <c r="C235" s="25"/>
-      <c r="D235" s="26">
+      <c r="B235" s="15"/>
+      <c r="C235" s="19"/>
+      <c r="D235" s="20">
         <f>SUM(D202:D234)</f>
         <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A236" s="21" t="s">
+      <c r="A236" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B236" s="19"/>
-      <c r="C236" s="23"/>
-      <c r="D236" s="26">
+      <c r="B236" s="13"/>
+      <c r="C236" s="17"/>
+      <c r="D236" s="20">
         <f>D197</f>
         <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A237" s="21" t="s">
+      <c r="A237" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B237" s="21"/>
-      <c r="C237" s="25"/>
-      <c r="D237" s="26">
+      <c r="B237" s="15"/>
+      <c r="C237" s="19"/>
+      <c r="D237" s="20">
         <f>D235+D236</f>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A238" s="27" t="s">
+      <c r="A238" s="21" t="s">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="M2:T2"/>
-    <mergeCell ref="A69:B69"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="Q3:R3"/>
